--- a/frontend/public/import-samples/sample.xlsx
+++ b/frontend/public/import-samples/sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Vocabulary" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,19 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="45.83203125" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,108 +428,44 @@
         <v>ex2_vi</v>
       </c>
       <c r="J1" t="str">
-        <v>tags</v>
+        <v>fill_en</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>abide by</v>
+        <v>achieve</v>
       </c>
       <c r="B2" t="str">
-        <v>tuân theo (quy định)</v>
+        <v>??t ???c</v>
       </c>
       <c r="C2" t="str">
         <v>verb</v>
       </c>
       <c r="D2" t="str">
-        <v>əˈbaɪd baɪ</v>
+        <v>/??t?i?v/</v>
       </c>
       <c r="E2" t="str">
-        <v>Ghi nhớ: abide by + rules</v>
+        <v>Often used with goals or results.</v>
       </c>
       <c r="F2" t="str">
-        <v>You must abide by the safety rules.</v>
+        <v>We achieve goals through steady work today.</v>
       </c>
       <c r="G2" t="str">
-        <v>Bạn phải tuân thủ các quy tắc an toàn.</v>
+        <v>Ch?ng t?i ??t m?c ti?u b?ng n? l?c ??u ??n h?m nay.</v>
       </c>
       <c r="H2" t="str">
-        <v>All employees should abide by company policies.</v>
+        <v>The team can achieve a better result today.</v>
       </c>
       <c r="I2" t="str">
-        <v>Mọi nhân viên nên tuân thủ chính sách công ty.</v>
+        <v>Nh?m c? th? ??t k?t qu? t?t h?n h?m nay.</v>
       </c>
       <c r="J2" t="str">
-        <v>phrasal,common</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>abundant</v>
-      </c>
-      <c r="B3" t="str">
-        <v>dồi dào, phong phú</v>
-      </c>
-      <c r="C3" t="str">
-        <v>adj</v>
-      </c>
-      <c r="D3" t="str">
-        <v>əˈbʌndənt</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Thường đi với resources/amount</v>
-      </c>
-      <c r="F3" t="str">
-        <v>The region has abundant fresh water.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Khu vực này có nguồn nước dồi dào.</v>
-      </c>
-      <c r="H3" t="str">
-        <v>We enjoyed an abundant meal.</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Chúng tôi thưởng thức một bữa ăn thịnh soạn.</v>
-      </c>
-      <c r="J3" t="str">
-        <v>common</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>accommodate</v>
-      </c>
-      <c r="B4" t="str">
-        <v>cung cấp chỗ ở</v>
-      </c>
-      <c r="C4" t="str">
-        <v>verb</v>
-      </c>
-      <c r="D4" t="str">
-        <v>əˈkɒmədeɪt</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Hotels accommodate guests</v>
-      </c>
-      <c r="F4" t="str">
-        <v>The hostel can accommodate fifty students.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Ký túc xá có thể chứa 50 sinh viên.</v>
-      </c>
-      <c r="H4" t="str">
-        <v>The hotel can accommodate large conferences.</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Khách sạn có thể tổ chức hội nghị lớn.</v>
-      </c>
-      <c r="J4" t="str">
-        <v>travel</v>
+        <v>She will achieve success through daily practice.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>